--- a/LubanConfig/MiniTemplate/Datas/生成数据/#角色成长数据_1导.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/生成数据/#角色成长数据_1导.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="士兵" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="弓箭手" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="弓" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="士兵" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="弓箭手" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -443,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.6" customWidth="1" min="2" max="2"/>
@@ -462,6 +463,7 @@
     <col width="15.4" customWidth="1" min="15" max="15"/>
     <col width="13.2" customWidth="1" min="16" max="16"/>
     <col width="24.2" customWidth="1" min="17" max="17"/>
+    <col width="13.2" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -550,6 +552,11 @@
           <t>技能解锁后的总战力</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>对塔伤害</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -637,6 +644,11 @@
           <t>float</t>
         </is>
       </c>
+      <c r="R2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -724,1085 +736,1150 @@
           <t>技能解锁后的总战力</t>
         </is>
       </c>
+      <c r="R3" s="1" t="inlineStr">
+        <is>
+          <t>对塔伤害</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>士兵,1</t>
+          <t>弓,1</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>13.3</v>
+        <v>62.5</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>13.3</v>
+        <v>81.2</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>93.09999999999999</v>
+        <v>568.8</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0</v>
+        <v>170.6</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>243.1</v>
+        <v>789.4</v>
       </c>
       <c r="O4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>大盾牌</t>
+          <t>穿透射击</t>
         </is>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>264.7</v>
+        <v>960</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>士兵,2</t>
+          <t>弓,2</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>150</v>
+        <v>62.5</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>16.6</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>16.6</v>
+        <v>101.6</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>150</v>
+        <v>62.5</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>116.4</v>
+        <v>710.9</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0</v>
+        <v>213.3</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>303.9</v>
+        <v>986.7</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>大盾牌</t>
+          <t>穿透射击</t>
         </is>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>330.9</v>
+        <v>1200</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>士兵,3</t>
+          <t>弓,3</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>187.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>20.8</v>
+        <v>97.7</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>20.8</v>
+        <v>127</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>187.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>145.5</v>
+        <v>888.7</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>46.9</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0</v>
+        <v>266.6</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>379.8</v>
+        <v>1233.4</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>大盾牌,格挡</t>
+          <t>穿透射击,满弓</t>
         </is>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>413.6</v>
+        <v>1642.2</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>士兵,4</t>
+          <t>弓,4</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>234.4</v>
+        <v>97.7</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>26</v>
+        <v>122.1</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>26</v>
+        <v>158.7</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>234.4</v>
+        <v>97.7</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>181.8</v>
+        <v>1110.8</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>58.6</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>333.3</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>474.8</v>
+        <v>1541.7</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>大盾牌,格挡</t>
+          <t>穿透射击,满弓</t>
         </is>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>517</v>
+        <v>2052.7</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>士兵,5</t>
+          <t>弓,5</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>293</v>
+        <v>122.1</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>32.5</v>
+        <v>152.6</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>32.5</v>
+        <v>198.4</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>293</v>
+        <v>122.1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>227.3</v>
+        <v>1388.5</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>73.2</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0</v>
+        <v>416.6</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>593.5</v>
+        <v>1927.2</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>大盾牌,格挡,酒足饭饱</t>
+          <t>穿透射击,满弓,精准射击</t>
         </is>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>771.9</v>
+        <v>3787.8</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>士兵,6</t>
+          <t>弓,6</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v>6</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>366.2</v>
+        <v>152.6</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>40.6</v>
+        <v>190.7</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>40.6</v>
+        <v>248</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>366.2</v>
+        <v>152.6</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>284.1</v>
+        <v>1735.7</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>91.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0</v>
+        <v>520.7</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>741.9</v>
+        <v>2409</v>
       </c>
       <c r="O9" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>大盾牌,格挡,酒足饭饱</t>
+          <t>穿透射击,满弓,精准射击</t>
         </is>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>964.9</v>
+        <v>4734.8</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>士兵,7</t>
+          <t>弓,7</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v>7</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>457.8</v>
+        <v>190.7</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>50.7</v>
+        <v>238.4</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>50.7</v>
+        <v>309.9</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>457.8</v>
+        <v>190.7</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>355.1</v>
+        <v>2169.6</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>114.4</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0</v>
+        <v>650.9</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>927.4</v>
+        <v>3011.2</v>
       </c>
       <c r="O10" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>大盾牌,格挡,酒足饭饱,越战越勇</t>
+          <t>穿透射击,满弓,精准射击,火焰箭</t>
         </is>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>1383.7</v>
+        <v>6992.5</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>士兵,8</t>
+          <t>弓,8</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v>8</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>572.2</v>
+        <v>238.4</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>63.4</v>
+        <v>298</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>63.4</v>
+        <v>387.4</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>572.2</v>
+        <v>238.4</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>443.9</v>
+        <v>2712</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>143.1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>0</v>
+        <v>813.6</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>1159.2</v>
+        <v>3764</v>
       </c>
       <c r="O11" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>大盾牌,格挡,酒足饭饱,越战越勇</t>
+          <t>穿透射击,满弓,精准射击,火焰箭</t>
         </is>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>1729.6</v>
+        <v>8740.6</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>士兵,9</t>
+          <t>弓,9</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v>9</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>715.3</v>
+        <v>298</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>79.3</v>
+        <v>372.5</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>79.3</v>
+        <v>484.3</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>715.3</v>
+        <v>298</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>554.9</v>
+        <v>3390</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>178.8</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>0</v>
+        <v>1017</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>1449</v>
+        <v>4705</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>大盾牌,格挡,酒足饭饱,越战越勇,一夫当关</t>
+          <t>穿透射击,满弓,精准射击,火焰箭,加速射击</t>
         </is>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>2428</v>
+        <v>12519.9</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>士兵,10</t>
+          <t>弓,10</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v>10</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>894.1</v>
+        <v>372.5</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>465.7</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>605.4</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>894.1</v>
+        <v>372.5</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>693.6</v>
+        <v>4237.5</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>223.5</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>0</v>
+        <v>1271.3</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>1811.2</v>
+        <v>5881.3</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>大盾牌,格挡,酒足饭饱,越战越勇,一夫当关</t>
+          <t>穿透射击,满弓,精准射击,火焰箭,加速射击</t>
         </is>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>3035</v>
+        <v>15649.8</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>士兵,11</t>
+          <t>弓,11</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v>11</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1117.6</v>
+        <v>465.7</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>123.9</v>
+        <v>582.1</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>123.9</v>
+        <v>756.7</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1117.6</v>
+        <v>465.7</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>867.1</v>
+        <v>5296.9</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>279.4</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>0</v>
+        <v>1589.1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>2264</v>
+        <v>7351.6</v>
       </c>
       <c r="O14" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>大盾牌,格挡,酒足饭饱,越战越勇,一夫当关</t>
+          <t>穿透射击,满弓,精准射击,火焰箭,加速射击</t>
         </is>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>3793.7</v>
+        <v>19562.3</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>士兵,12</t>
+          <t>弓,12</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v>12</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1397</v>
+        <v>582.1</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>154.8</v>
+        <v>727.6</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>154.8</v>
+        <v>945.9</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1397</v>
+        <v>582.1</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1083.8</v>
+        <v>6621.1</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>349.2</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0</v>
+        <v>1986.3</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>2830.1</v>
+        <v>9189.5</v>
       </c>
       <c r="O15" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>大盾牌,格挡,酒足饭饱,越战越勇,一夫当关,不屈</t>
+          <t>穿透射击,满弓,精准射击,火焰箭,加速射击,毒箭</t>
         </is>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>4742.1</v>
+        <v>27279.7</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>士兵,13</t>
+          <t>弓,13</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v>13</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1746.2</v>
+        <v>727.6</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>193.5</v>
+        <v>909.5</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>193.5</v>
+        <v>1182.3</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1746.2</v>
+        <v>727.6</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1354.8</v>
+        <v>8276.4</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>436.6</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>0</v>
+        <v>2482.9</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>3537.6</v>
+        <v>11486.9</v>
       </c>
       <c r="O16" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>大盾牌,格挡,酒足饭饱,越战越勇,一夫当关,不屈</t>
+          <t>穿透射击,满弓,精准射击,火焰箭,加速射击,毒箭</t>
         </is>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>5927.7</v>
+        <v>34099.6</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>士兵,14</t>
+          <t>弓,14</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v>14</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>2182.8</v>
+        <v>909.5</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>241.9</v>
+        <v>1136.9</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>241.9</v>
+        <v>1477.9</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>2182.8</v>
+        <v>909.5</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1693.5</v>
+        <v>10345.5</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>545.7</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>0</v>
+        <v>3103.7</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>4422</v>
+        <v>14358.6</v>
       </c>
       <c r="O17" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>大盾牌,格挡,酒足饭饱,越战越勇,一夫当关,不屈</t>
+          <t>穿透射击,满弓,精准射击,火焰箭,加速射击,毒箭</t>
         </is>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>7409.6</v>
+        <v>42624.5</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>士兵,15</t>
+          <t>弓,15</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v>15</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>2728.5</v>
+        <v>1136.9</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>302.4</v>
+        <v>1421.1</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>302.4</v>
+        <v>1847.4</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2728.5</v>
+        <v>1136.9</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>2116.8</v>
+        <v>12931.9</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>682.1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>0</v>
+        <v>3879.6</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>5527.5</v>
+        <v>17948.3</v>
       </c>
       <c r="O18" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>大盾牌,格挡,酒足饭饱,越战越勇,一夫当关,不屈,向死而生</t>
+          <t>穿透射击,满弓,精准射击,火焰箭,加速射击,毒箭,直击要害</t>
         </is>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>12922.5</v>
+        <v>71776.3</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>士兵,16</t>
+          <t>弓,16</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v>16</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>3410.6</v>
+        <v>1421.1</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>378</v>
+        <v>1776.4</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>378</v>
+        <v>2309.3</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>3410.6</v>
+        <v>1421.1</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>2646.1</v>
+        <v>16164.8</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>852.7</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>0</v>
+        <v>4849.5</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>6909.3</v>
+        <v>22435.4</v>
       </c>
       <c r="O19" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>大盾牌,格挡,酒足饭饱,越战越勇,一夫当关,不屈,向死而生</t>
+          <t>穿透射击,满弓,精准射击,火焰箭,加速射击,毒箭,直击要害</t>
         </is>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>16153.1</v>
+        <v>89720.39999999999</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>士兵,17</t>
+          <t>弓,17</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v>17</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>4263.3</v>
+        <v>1776.4</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>472.5</v>
+        <v>2220.4</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>472.5</v>
+        <v>2886.6</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>4263.3</v>
+        <v>1776.4</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>3307.6</v>
+        <v>20206.1</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1065.8</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>0</v>
+        <v>6061.8</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>8636.6</v>
+        <v>28044.2</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>大盾牌,格挡,酒足饭饱,越战越勇,一夫当关,不屈,向死而生</t>
+          <t>穿透射击,满弓,精准射击,火焰箭,加速射击,毒箭,直击要害</t>
         </is>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>20191.4</v>
+        <v>112150.5</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>士兵,18</t>
+          <t>弓,18</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v>18</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>5329.1</v>
+        <v>2220.4</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>590.6</v>
+        <v>2775.6</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>590.6</v>
+        <v>3608.2</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>5329.1</v>
+        <v>2220.4</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>4134.5</v>
+        <v>25257.6</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>1332.3</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>0</v>
+        <v>7577.3</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>10795.8</v>
+        <v>35055.3</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>大盾牌,格挡,酒足饭饱,越战越勇,一夫当关,不屈,向死而生</t>
+          <t>穿透射击,满弓,精准射击,火焰箭,加速射击,毒箭,直击要害</t>
         </is>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>25239.3</v>
+        <v>140188.1</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>士兵,19</t>
+          <t>弓,19</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>19</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>6661.3</v>
+        <v>2775.6</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>738.3</v>
+        <v>3469.4</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>738.3</v>
+        <v>4510.3</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>6661.3</v>
+        <v>2775.6</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>5168.1</v>
+        <v>31572</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1665.3</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>0</v>
+        <v>9471.6</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>13494.8</v>
+        <v>43819.1</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>大盾牌,格挡,酒足饭饱,越战越勇,一夫当关,不屈,向死而生</t>
+          <t>穿透射击,满弓,精准射击,火焰箭,加速射击,毒箭,直击要害</t>
         </is>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>31549.1</v>
+        <v>175235.2</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>士兵,20</t>
+          <t>弓,20</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v>20</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>8326.700000000001</v>
+        <v>3469.4</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>922.9</v>
+        <v>4336.8</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>922.9</v>
+        <v>5637.9</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>8326.700000000001</v>
+        <v>3469.4</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>6460.1</v>
+        <v>39465</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>2081.7</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>0</v>
+        <v>11839.5</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>16868.5</v>
+        <v>54773.9</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>大盾牌,格挡,酒足饭饱,越战越勇,一夫当关,不屈,向死而生</t>
+          <t>穿透射击,满弓,精准射击,火焰箭,加速射击,毒箭,直击要害</t>
         </is>
       </c>
       <c r="Q23" s="2" t="n">
-        <v>39436.4</v>
+        <v>219043.9</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1816,7 +1893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.6" customWidth="1" min="2" max="2"/>
@@ -1835,6 +1912,7 @@
     <col width="15.4" customWidth="1" min="15" max="15"/>
     <col width="13.2" customWidth="1" min="16" max="16"/>
     <col width="24.2" customWidth="1" min="17" max="17"/>
+    <col width="13.2" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1923,6 +2001,11 @@
           <t>技能解锁后的总战力</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>对塔伤害</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -2010,6 +2093,11 @@
           <t>float</t>
         </is>
       </c>
+      <c r="R2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -2097,10 +2185,1464 @@
           <t>技能解锁后的总战力</t>
         </is>
       </c>
+      <c r="R3" s="1" t="inlineStr">
+        <is>
+          <t>对塔伤害</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>士兵,1</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>243.1</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>大盾牌</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>264.7</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>士兵,2</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>116.4</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>303.9</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>大盾牌</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>330.9</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>士兵,3</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>379.8</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>大盾牌,格挡</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>413.6</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>士兵,4</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>234.4</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>234.4</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>181.8</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>474.8</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>大盾牌,格挡</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>517</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>士兵,5</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>293</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>293</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>227.3</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>593.5</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>大盾牌,格挡,酒足饭饱</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>771.9</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>士兵,6</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>366.2</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>366.2</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>284.1</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>741.9</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>大盾牌,格挡,酒足饭饱</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>964.9</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>士兵,7</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>457.8</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>457.8</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>355.1</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>114.4</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>927.4</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>大盾牌,格挡,酒足饭饱,越战越勇</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>1383.7</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>士兵,8</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>572.2</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>572.2</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>443.9</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>143.1</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>1159.2</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>大盾牌,格挡,酒足饭饱,越战越勇</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>1729.6</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>士兵,9</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>715.3</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>715.3</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>554.9</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>178.8</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>1449</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>大盾牌,格挡,酒足饭饱,越战越勇,一夫当关</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>2428</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>士兵,10</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>894.1</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>894.1</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>693.6</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>223.5</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>1811.2</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>大盾牌,格挡,酒足饭饱,越战越勇,一夫当关</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>3035</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>士兵,11</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>1117.6</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>1117.6</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>867.1</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>279.4</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>2264</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>大盾牌,格挡,酒足饭饱,越战越勇,一夫当关</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>3793.7</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>士兵,12</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>1397</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>154.8</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>154.8</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>1397</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>1083.8</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>349.2</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>2830.1</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>大盾牌,格挡,酒足饭饱,越战越勇,一夫当关,不屈</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>4742.1</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>士兵,13</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>1746.2</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>193.5</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>193.5</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>1746.2</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>1354.8</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>436.6</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>3537.6</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>大盾牌,格挡,酒足饭饱,越战越勇,一夫当关,不屈</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>5927.7</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>士兵,14</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>2182.8</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>241.9</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>241.9</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>2182.8</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>1693.5</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>545.7</v>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>4422</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>大盾牌,格挡,酒足饭饱,越战越勇,一夫当关,不屈</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>7409.6</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>士兵,15</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>2728.5</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>302.4</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>302.4</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>2728.5</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>2116.8</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>682.1</v>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>5527.5</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>大盾牌,格挡,酒足饭饱,越战越勇,一夫当关,不屈,向死而生</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>12922.5</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>士兵,16</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>3410.6</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>378</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>378</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>3410.6</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>2646.1</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>852.7</v>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>6909.3</v>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>大盾牌,格挡,酒足饭饱,越战越勇,一夫当关,不屈,向死而生</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>16153.1</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>士兵,17</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>4263.3</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>472.5</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>472.5</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>4263.3</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>3307.6</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>1065.8</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>8636.6</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>大盾牌,格挡,酒足饭饱,越战越勇,一夫当关,不屈,向死而生</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>20191.4</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>士兵,18</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>5329.1</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>590.6</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>590.6</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>5329.1</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>4134.5</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>1332.3</v>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>10795.8</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>大盾牌,格挡,酒足饭饱,越战越勇,一夫当关,不屈,向死而生</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>25239.3</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>士兵,19</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>6661.3</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>738.3</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>738.3</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>6661.3</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>5168.1</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>1665.3</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>13494.8</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>大盾牌,格挡,酒足饭饱,越战越勇,一夫当关,不屈,向死而生</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>31549.1</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>士兵,20</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>8326.700000000001</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>922.9</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>922.9</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>8326.700000000001</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>6460.1</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>2081.7</v>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>16868.5</v>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>大盾牌,格挡,酒足饭饱,越战越勇,一夫当关,不屈,向死而生</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>39436.4</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17.6" customWidth="1" min="2" max="2"/>
+    <col width="8.800000000000001" customWidth="1" min="3" max="3"/>
+    <col width="8.800000000000001" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="17.6" customWidth="1" min="6" max="6"/>
+    <col width="17.6" customWidth="1" min="7" max="7"/>
+    <col width="17.6" customWidth="1" min="8" max="8"/>
+    <col width="15.4" customWidth="1" min="9" max="9"/>
+    <col width="13.2" customWidth="1" min="10" max="10"/>
+    <col width="15.4" customWidth="1" min="11" max="11"/>
+    <col width="17.6" customWidth="1" min="12" max="12"/>
+    <col width="19.8" customWidth="1" min="13" max="13"/>
+    <col width="15.4" customWidth="1" min="14" max="14"/>
+    <col width="15.4" customWidth="1" min="15" max="15"/>
+    <col width="13.2" customWidth="1" min="16" max="16"/>
+    <col width="24.2" customWidth="1" min="17" max="17"/>
+    <col width="13.2" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>角色名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>血量</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>攻击力</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>攻击速度_S</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>攻击范围_格</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>移速_格_S</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>基础DPS</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>血量战力</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>DPS战力</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>血量特效战力</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>DPS特效战力</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>基础总战力</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>解锁技能数</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>技能列表</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>技能解锁后的总战力</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>对塔伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="P2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="R2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>角色名称</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>血量</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>攻击力</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>攻击速度_S</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>攻击范围_格</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>移速_格_S</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>基础DPS</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>血量战力</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>DPS战力</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>血量特效战力</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>DPS特效战力</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>基础总战力</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>解锁技能数</t>
+        </is>
+      </c>
+      <c r="P3" s="1" t="inlineStr">
+        <is>
+          <t>技能列表</t>
+        </is>
+      </c>
+      <c r="Q3" s="1" t="inlineStr">
+        <is>
+          <t>技能解锁后的总战力</t>
+        </is>
+      </c>
+      <c r="R3" s="1" t="inlineStr">
+        <is>
+          <t>对塔伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>弓箭手,1</t>
         </is>
       </c>
@@ -2151,6 +3693,9 @@
       <c r="Q4" s="2" t="n">
         <v>960</v>
       </c>
+      <c r="R4" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -2205,6 +3750,9 @@
       <c r="Q5" s="2" t="n">
         <v>1200</v>
       </c>
+      <c r="R5" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
@@ -2259,6 +3807,9 @@
       <c r="Q6" s="2" t="n">
         <v>1642.2</v>
       </c>
+      <c r="R6" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
@@ -2313,6 +3864,9 @@
       <c r="Q7" s="2" t="n">
         <v>2052.7</v>
       </c>
+      <c r="R7" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -2367,6 +3921,9 @@
       <c r="Q8" s="2" t="n">
         <v>3787.8</v>
       </c>
+      <c r="R8" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
@@ -2421,6 +3978,9 @@
       <c r="Q9" s="2" t="n">
         <v>4734.8</v>
       </c>
+      <c r="R9" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
@@ -2475,6 +4035,9 @@
       <c r="Q10" s="2" t="n">
         <v>6992.5</v>
       </c>
+      <c r="R10" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
@@ -2529,6 +4092,9 @@
       <c r="Q11" s="2" t="n">
         <v>8740.6</v>
       </c>
+      <c r="R11" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
@@ -2583,6 +4149,9 @@
       <c r="Q12" s="2" t="n">
         <v>12519.9</v>
       </c>
+      <c r="R12" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="2" t="inlineStr">
@@ -2637,6 +4206,9 @@
       <c r="Q13" s="2" t="n">
         <v>15649.8</v>
       </c>
+      <c r="R13" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
@@ -2691,6 +4263,9 @@
       <c r="Q14" s="2" t="n">
         <v>19562.3</v>
       </c>
+      <c r="R14" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
@@ -2745,6 +4320,9 @@
       <c r="Q15" s="2" t="n">
         <v>27279.7</v>
       </c>
+      <c r="R15" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
@@ -2799,6 +4377,9 @@
       <c r="Q16" s="2" t="n">
         <v>34099.6</v>
       </c>
+      <c r="R16" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
@@ -2853,6 +4434,9 @@
       <c r="Q17" s="2" t="n">
         <v>42624.5</v>
       </c>
+      <c r="R17" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="2" t="inlineStr">
@@ -2907,6 +4491,9 @@
       <c r="Q18" s="2" t="n">
         <v>71776.3</v>
       </c>
+      <c r="R18" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
@@ -2961,6 +4548,9 @@
       <c r="Q19" s="2" t="n">
         <v>89720.39999999999</v>
       </c>
+      <c r="R19" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="B20" s="2" t="inlineStr">
@@ -3015,6 +4605,9 @@
       <c r="Q20" s="2" t="n">
         <v>112150.5</v>
       </c>
+      <c r="R20" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="B21" s="2" t="inlineStr">
@@ -3069,6 +4662,9 @@
       <c r="Q21" s="2" t="n">
         <v>140188.1</v>
       </c>
+      <c r="R21" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
@@ -3123,6 +4719,9 @@
       <c r="Q22" s="2" t="n">
         <v>175235.2</v>
       </c>
+      <c r="R22" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="B23" s="2" t="inlineStr">
@@ -3176,6 +4775,9 @@
       </c>
       <c r="Q23" s="2" t="n">
         <v>219043.9</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
